--- a/artfynd/A 34119-2023 artfynd.xlsx
+++ b/artfynd/A 34119-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34119-2023 artfynd.xlsx
+++ b/artfynd/A 34119-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111759558</v>
+        <v>111759195</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565478</v>
+        <v>565516</v>
       </c>
       <c r="R2" t="n">
-        <v>6417132</v>
+        <v>6416937</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111759379</v>
+        <v>111759175</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565496</v>
+        <v>565565</v>
       </c>
       <c r="R3" t="n">
-        <v>6416993</v>
+        <v>6416937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111759541</v>
+        <v>111759379</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,8 +922,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565468</v>
+        <v>565496</v>
       </c>
       <c r="R4" t="n">
-        <v>6417115</v>
+        <v>6416993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111759664</v>
+        <v>111759441</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,7 +1042,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1064,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565559</v>
+        <v>565472</v>
       </c>
       <c r="R5" t="n">
-        <v>6417044</v>
+        <v>6417103</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1091,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111759175</v>
+        <v>111759455</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,7 +1153,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1179,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565565</v>
+        <v>565456</v>
       </c>
       <c r="R6" t="n">
-        <v>6416937</v>
+        <v>6417100</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111759441</v>
+        <v>111759468</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1263,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1298,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565472</v>
+        <v>565446</v>
       </c>
       <c r="R7" t="n">
-        <v>6417103</v>
+        <v>6417123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1324,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 blommor</t>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,15 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111759572</v>
+        <v>111759485</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,21 +1380,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 34711, Jössebäck, Sm</t>
+          <t>A 34119, Jössebäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565514</v>
+        <v>565467</v>
       </c>
       <c r="R8" t="n">
-        <v>6417097</v>
+        <v>6417129</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,15 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111759468</v>
+        <v>111759541</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,21 +1490,9 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565446</v>
+        <v>565468</v>
       </c>
       <c r="R9" t="n">
-        <v>6417123</v>
+        <v>6417115</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,11 +1537,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,15 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111759455</v>
+        <v>111759558</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565456</v>
+        <v>565478</v>
       </c>
       <c r="R10" t="n">
-        <v>6417100</v>
+        <v>6417132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,15 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111759485</v>
+        <v>111759572</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,29 +1702,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 34119, Jössebäck, Sm</t>
+          <t>A 34711, Jössebäck, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565467</v>
+        <v>565514</v>
       </c>
       <c r="R11" t="n">
-        <v>6417129</v>
+        <v>6417097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,50 +1776,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111759195</v>
+        <v>111759664</v>
       </c>
       <c r="B12" t="n">
-        <v>90021</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1878,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565516</v>
+        <v>565559</v>
       </c>
       <c r="R12" t="n">
-        <v>6416937</v>
+        <v>6417044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,6 +1883,116 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111759226</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 34119, Jössebäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>565489</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6416949</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
